--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N64_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N64_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.42281192254453</v>
+        <v>5.756206937413487</v>
       </c>
       <c r="D2" t="n">
-        <v>12.22952832548108</v>
+        <v>1.987298352890675</v>
       </c>
       <c r="E2" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F2" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>21.10003282531813</v>
+        <v>3.428755334114196</v>
       </c>
       <c r="D3" t="n">
-        <v>21.98932149087854</v>
+        <v>3.573264742267762</v>
       </c>
       <c r="E3" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F3" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.65342935651962</v>
+        <v>2.868682270434439</v>
       </c>
       <c r="D4" t="n">
-        <v>17.46216061558352</v>
+        <v>2.837601100032322</v>
       </c>
       <c r="E4" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F4" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>22.12552667831427</v>
+        <v>3.595398085226068</v>
       </c>
       <c r="D5" t="n">
-        <v>21.4953703203366</v>
+        <v>3.492997677054698</v>
       </c>
       <c r="E5" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F5" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.81074715289681</v>
+        <v>5.494246412345731</v>
       </c>
       <c r="D6" t="n">
-        <v>22.92812917526507</v>
+        <v>3.725820990980574</v>
       </c>
       <c r="E6" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F6" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.04697129723009</v>
+        <v>5.53263283579989</v>
       </c>
       <c r="D7" t="n">
-        <v>33.16165777223952</v>
+        <v>5.388769387988923</v>
       </c>
       <c r="E7" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F7" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>35.8775079385391</v>
+        <v>5.830095040012605</v>
       </c>
       <c r="D8" t="n">
-        <v>35.24267328212354</v>
+        <v>5.726934408345076</v>
       </c>
       <c r="E8" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F8" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.73592693817323</v>
+        <v>4.994588127453151</v>
       </c>
       <c r="D9" t="n">
-        <v>34.6958562091137</v>
+        <v>5.638076633980976</v>
       </c>
       <c r="E9" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F9" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>16.4306805515753</v>
+        <v>2.669985589630986</v>
       </c>
       <c r="D10" t="n">
-        <v>18.07968821576233</v>
+        <v>2.937949335061378</v>
       </c>
       <c r="E10" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F10" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>39.74182008432636</v>
+        <v>6.458045763703034</v>
       </c>
       <c r="D11" t="n">
-        <v>33.11658803604431</v>
+        <v>5.3814455558572</v>
       </c>
       <c r="E11" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F11" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>28.02705598557525</v>
+        <v>4.554396597655979</v>
       </c>
       <c r="D12" t="n">
-        <v>21.45508367978824</v>
+        <v>3.48645109796559</v>
       </c>
       <c r="E12" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F12" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.78325181395805</v>
+        <v>3.377278419768183</v>
       </c>
       <c r="D13" t="n">
-        <v>24.24999936224077</v>
+        <v>3.940624896364126</v>
       </c>
       <c r="E13" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F13" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>23.18164262935445</v>
+        <v>3.767016927270098</v>
       </c>
       <c r="D14" t="n">
-        <v>14.75080455013153</v>
+        <v>2.397005739396374</v>
       </c>
       <c r="E14" t="n">
-        <v>7.489410133816055</v>
+        <v>1.217029146745109</v>
       </c>
       <c r="F14" t="n">
-        <v>7.481442331560578</v>
+        <v>1.215734378878594</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
